--- a/fuction_ensemble_1/redes-ensemble-s/Teste02 copy/content/results/metrics_2_0.xlsx
+++ b/fuction_ensemble_1/redes-ensemble-s/Teste02 copy/content/results/metrics_2_0.xlsx
@@ -513,1321 +513,1321 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_23</t>
+          <t>model_2_0_1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8257812370964386</v>
+        <v>0.7443947356610541</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3891436716441321</v>
+        <v>0.577999229344732</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02522268572038722</v>
+        <v>0.09583181126843543</v>
       </c>
       <c r="E2" t="n">
-        <v>0.832100329449726</v>
+        <v>0.9892527130070606</v>
       </c>
       <c r="F2" t="n">
-        <v>0.496496421653</v>
+        <v>0.8746881095346769</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1034237835182462</v>
+        <v>0.1517383264840922</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3626307041314466</v>
+        <v>0.2505178869450652</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3059758988850096</v>
+        <v>0.09589964234213506</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01959724536233647</v>
+        <v>0.007042055644465979</v>
       </c>
       <c r="K2" t="n">
-        <v>0.162786572123673</v>
+        <v>0.05147084899330052</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1695315589703199</v>
+        <v>0.2123242290496129</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3215956833016361</v>
+        <v>0.3895360400323598</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5354166322571696</v>
+        <v>0.3183859617628109</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3352866773346262</v>
+        <v>0.4061193957073036</v>
       </c>
       <c r="P2" t="n">
-        <v>34.53784065734779</v>
+        <v>33.77119555594244</v>
       </c>
       <c r="Q2" t="n">
-        <v>52.8209780303708</v>
+        <v>52.05433292896545</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_18</t>
+          <t>model_2_0_2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8252370621297334</v>
+        <v>0.7941391474913195</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3856019410255506</v>
+        <v>0.4777791440861984</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01714746856496596</v>
+        <v>-0.283492854989601</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8151735817564484</v>
+        <v>0.9933594886244465</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4971681420492766</v>
+        <v>0.8289881933222196</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1037468292856171</v>
+        <v>0.1222078947749442</v>
       </c>
       <c r="H3" t="n">
-        <v>0.364733228421433</v>
+        <v>0.3100128588367918</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3035658645946686</v>
+        <v>0.1361323117492815</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02157293493125791</v>
+        <v>0.004351130722114234</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1625693997629633</v>
+        <v>0.07024172123569788</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1726144231329846</v>
+        <v>0.210759558485923</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3220975462272525</v>
+        <v>0.3495824577620339</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5339654990126224</v>
+        <v>0.4510377266435188</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3358099056039855</v>
+        <v>0.364464906724413</v>
       </c>
       <c r="P3" t="n">
-        <v>34.53160336288163</v>
+        <v>34.20406325794374</v>
       </c>
       <c r="Q3" t="n">
-        <v>52.81474073590464</v>
+        <v>52.48720063096675</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_20</t>
+          <t>model_2_0_3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8267816605254739</v>
+        <v>0.8065170467092044</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3800566004164618</v>
+        <v>0.4761756743257974</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.004369773748876371</v>
+        <v>-0.6370492034461848</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8208780313943866</v>
+        <v>0.9725317203991835</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5040954499681296</v>
+        <v>0.7667267484352546</v>
       </c>
       <c r="G4" t="n">
-        <v>0.102829888954729</v>
+        <v>0.1148598391018027</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3680251821532294</v>
+        <v>0.3109647477528528</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2997523841562367</v>
+        <v>0.1736318917912906</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02090711171168053</v>
+        <v>0.01799832399877102</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1603297479339586</v>
+        <v>0.09581510789503081</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1720389926544875</v>
+        <v>0.1845405985280901</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3206709979944071</v>
+        <v>0.3389097801802166</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5380844280679303</v>
+        <v>0.4840454578912119</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3343226262595059</v>
+        <v>0.3533378711624494</v>
       </c>
       <c r="P4" t="n">
-        <v>34.54935843926679</v>
+        <v>34.32808536873414</v>
       </c>
       <c r="Q4" t="n">
-        <v>52.8324958122898</v>
+        <v>52.61122274175715</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_16</t>
+          <t>model_2_0_4</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8200171125869081</v>
+        <v>0.8021233881146728</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3677083180817228</v>
+        <v>0.4459261729882819</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06975619357879714</v>
+        <v>-0.8453950719742116</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8379538703666172</v>
+        <v>0.9473230282816206</v>
       </c>
       <c r="F5" t="n">
-        <v>0.476998397813621</v>
+        <v>0.7197194531501252</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1068456168243172</v>
+        <v>0.1174681046396855</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3753556559651527</v>
+        <v>0.3289221584572205</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3192668456103105</v>
+        <v>0.195729875910074</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01891402021239524</v>
+        <v>0.0345160751980006</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1690904329113529</v>
+        <v>0.1151229755540373</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1722399720240534</v>
+        <v>0.185005856495885</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3268724779242163</v>
+        <v>0.342736202697768</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5200456335650884</v>
+        <v>0.4723290349724607</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3407881160287603</v>
+        <v>0.3573271924083595</v>
       </c>
       <c r="P5" t="n">
-        <v>34.47274063964852</v>
+        <v>34.28317686424425</v>
       </c>
       <c r="Q5" t="n">
-        <v>52.75587801267153</v>
+        <v>52.56631423726726</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_1</t>
+          <t>model_2_0_5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6413697456375802</v>
+        <v>0.7976949835800353</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3543566060117365</v>
+        <v>0.4291636287058971</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1567343607380782</v>
+        <v>-0.957649628692969</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.007210462510630622</v>
+        <v>0.9256818525926123</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2842933537611114</v>
+        <v>0.6879643182475451</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2128984110098641</v>
+        <v>0.1200969968685616</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3832818090138265</v>
+        <v>0.3388731288474536</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3452253259001136</v>
+        <v>0.2076360367048991</v>
       </c>
       <c r="J6" t="n">
-        <v>0.117561580083166</v>
+        <v>0.04869624583211345</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2313934529916398</v>
+        <v>0.1281661412685063</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3062620602929232</v>
+        <v>0.1857005597375682</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4614091579172049</v>
+        <v>0.3465501361542966</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04365265503354721</v>
+        <v>0.4605199562134276</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4810523010183713</v>
+        <v>0.3613034929080632</v>
       </c>
       <c r="P6" t="n">
-        <v>33.09388034132431</v>
+        <v>34.23891111093288</v>
       </c>
       <c r="Q6" t="n">
-        <v>51.37701771434732</v>
+        <v>52.52204848395589</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_21</t>
+          <t>model_2_0_7</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.826028084212292</v>
+        <v>0.7980662546887846</v>
       </c>
       <c r="C7" t="n">
-        <v>0.349609659836837</v>
+        <v>0.4279668571680422</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.01576605318183555</v>
+        <v>-0.9455248926984627</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8216192579478643</v>
+        <v>0.9091266996113668</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4989692439537028</v>
+        <v>0.676324885650287</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1032772444070354</v>
+        <v>0.1198765943003312</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3860998013206444</v>
+        <v>0.3395835841301629</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3031535836146687</v>
+        <v>0.2063500394094211</v>
       </c>
       <c r="J7" t="n">
-        <v>0.020820595766831</v>
+        <v>0.05954384937830782</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1619870896907499</v>
+        <v>0.1329469443938645</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1705008357794875</v>
+        <v>0.1884796526612125</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3213677712637585</v>
+        <v>0.3462319949114049</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5360748912327787</v>
+        <v>0.4615100125034255</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3350490626094532</v>
+        <v>0.3609718077338185</v>
       </c>
       <c r="P7" t="n">
-        <v>34.54067642719823</v>
+        <v>34.24258489235407</v>
       </c>
       <c r="Q7" t="n">
-        <v>52.82381380022124</v>
+        <v>52.52572226537708</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_15</t>
+          <t>model_2_0_8</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8169595682222459</v>
+        <v>0.7943120594507271</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3079486360138403</v>
+        <v>0.4214882782034655</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07852496767225414</v>
+        <v>-0.9889566399461038</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7995533124504797</v>
+        <v>0.8779853856512432</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4660194792670023</v>
+        <v>0.6458780478038442</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1086607072382201</v>
+        <v>0.1221052467664321</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4108315847244974</v>
+        <v>0.3434295484635748</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3218838707432258</v>
+        <v>0.2109565817311388</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02339613237537192</v>
+        <v>0.07994889354369103</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1726400015592988</v>
+        <v>0.1454527376374149</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1740340248068596</v>
+        <v>0.1887786337418339</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3296372358187407</v>
+        <v>0.349435611760496</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5118921819259892</v>
+        <v>0.4514988252019391</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3436705753906925</v>
+        <v>0.3643118091845765</v>
       </c>
       <c r="P8" t="n">
-        <v>34.43905005830691</v>
+        <v>34.20574385545731</v>
       </c>
       <c r="Q8" t="n">
-        <v>52.72218743132992</v>
+        <v>52.48888122848032</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_22</t>
+          <t>model_2_0_6</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8276834300265173</v>
+        <v>0.7947369985777015</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2978752683493302</v>
+        <v>0.4186172304410365</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008320098122450936</v>
+        <v>-1.016595262711589</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8094776535295427</v>
+        <v>0.910110903053744</v>
       </c>
       <c r="F9" t="n">
-        <v>0.50789464527427</v>
+        <v>0.667933833792846</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1022945596244955</v>
+        <v>0.1218529845442457</v>
       </c>
       <c r="H9" t="n">
-        <v>0.416811570916976</v>
+        <v>0.3451339264381582</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2959651143204773</v>
+        <v>0.2138880430135331</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02223776353195195</v>
+        <v>0.05889895961112766</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1591014389262146</v>
+        <v>0.1363935013123304</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1693617776649593</v>
+        <v>0.1860519050611517</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3198352069808693</v>
+        <v>0.3490744684795004</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5404891467373796</v>
+        <v>0.4526319962072041</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3334512538921959</v>
+        <v>0.3639352912864391</v>
       </c>
       <c r="P9" t="n">
-        <v>34.55979757607982</v>
+        <v>34.20988001123678</v>
       </c>
       <c r="Q9" t="n">
-        <v>52.84293494910283</v>
+        <v>52.49301738425979</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_2</t>
+          <t>model_2_0_9</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6397784096658842</v>
+        <v>0.77566480553053</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2890484609318404</v>
+        <v>0.3992531554317957</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3594219803775811</v>
+        <v>-1.159358259402499</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6968665655418356</v>
+        <v>0.7796587334600513</v>
       </c>
       <c r="F10" t="n">
-        <v>0.06625274533520098</v>
+        <v>0.5454487449179961</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2138430967847975</v>
+        <v>0.1331750622128878</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4220515450982245</v>
+        <v>0.3566292778481288</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4057170878127778</v>
+        <v>0.2290300492165565</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1980582232417863</v>
+        <v>0.1443764794562406</v>
       </c>
       <c r="K10" t="n">
-        <v>0.301887655527282</v>
+        <v>0.1867032643363986</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2873376393213692</v>
+        <v>0.2008822000685092</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4624317212138431</v>
+        <v>0.3649315856607753</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0394090924423578</v>
+        <v>0.4017728147480799</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4821183969515452</v>
+        <v>0.3804674787748787</v>
       </c>
       <c r="P10" t="n">
-        <v>33.08502545094367</v>
+        <v>34.03218151805557</v>
       </c>
       <c r="Q10" t="n">
-        <v>51.36816282396668</v>
+        <v>52.31531889107858</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_19</t>
+          <t>model_2_0_10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8303455986940004</v>
+        <v>0.7342232600976846</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2882024773542957</v>
+        <v>0.3019726064489535</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08921064234936082</v>
+        <v>-1.613760905625173</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7027814839817494</v>
+        <v>0.598859533681372</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5259704080459553</v>
+        <v>0.3425687330062939</v>
       </c>
       <c r="G11" t="n">
-        <v>0.100714181303779</v>
+        <v>0.1577765537633743</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4225537574944427</v>
+        <v>0.4143792140252497</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2718234743374184</v>
+        <v>0.277225785137334</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03469133778255458</v>
+        <v>0.2628434028902975</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1532574060599865</v>
+        <v>0.2700345940138158</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1708925315129495</v>
+        <v>0.2089372845229081</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3173549768063816</v>
+        <v>0.3972109688356734</v>
       </c>
       <c r="N11" t="n">
-        <v>0.547588263184001</v>
+        <v>0.2912620269271589</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3308654351843961</v>
+        <v>0.4141210621190671</v>
       </c>
       <c r="P11" t="n">
-        <v>34.59093732385157</v>
+        <v>33.69315092718182</v>
       </c>
       <c r="Q11" t="n">
-        <v>52.87407469687458</v>
+        <v>51.97628830020483</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_17</t>
+          <t>model_2_0_11</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8277313284312571</v>
+        <v>0.7268803958244</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2736101128239835</v>
+        <v>0.2770375006872966</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05984169124867822</v>
+        <v>-1.688823454360369</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7152879503424581</v>
+        <v>0.5666697267729045</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5146725675633088</v>
+        <v>0.3072016496914834</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1022661250623386</v>
+        <v>0.1621355951912165</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4312164154369615</v>
+        <v>0.4291817699458523</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2805885858956229</v>
+        <v>0.2851872149539402</v>
       </c>
       <c r="J12" t="n">
-        <v>0.03323158334061107</v>
+        <v>0.2839354618985819</v>
       </c>
       <c r="K12" t="n">
-        <v>0.156910084618117</v>
+        <v>0.2845613384262611</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1712499636832837</v>
+        <v>0.2101614869647832</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3197907519962681</v>
+        <v>0.402660645197934</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5406168758166856</v>
+        <v>0.2716810555317334</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3334049063668657</v>
+        <v>0.4198027424864544</v>
       </c>
       <c r="P12" t="n">
-        <v>34.56035358834354</v>
+        <v>33.63864457298376</v>
       </c>
       <c r="Q12" t="n">
-        <v>52.84349096136655</v>
+        <v>51.92178194600677</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_3</t>
+          <t>model_2_0_12</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6307443395727999</v>
+        <v>0.707011087532418</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2704067288540226</v>
+        <v>0.242775697063</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4469984975042154</v>
+        <v>-1.953384870904364</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.012227661879515</v>
+        <v>0.4690055060940991</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.03109414838646263</v>
+        <v>0.1951435033640847</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2192061110435604</v>
+        <v>0.1739308749027637</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4331180825405126</v>
+        <v>0.4495210566100873</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4318541445929949</v>
+        <v>0.3132476416978745</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2348671625470865</v>
+        <v>0.3479289959826153</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3333606535700407</v>
+        <v>0.3305883188402449</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2768777600621706</v>
+        <v>0.211192753605919</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4681945226543775</v>
+        <v>0.4170502066931075</v>
       </c>
       <c r="N13" t="n">
-        <v>0.01531823886079964</v>
+        <v>0.2186962334197815</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4881265327800467</v>
+        <v>0.4348048974049761</v>
       </c>
       <c r="P13" t="n">
-        <v>33.03548569089705</v>
+        <v>33.49819465874856</v>
       </c>
       <c r="Q13" t="n">
-        <v>51.31862306392006</v>
+        <v>51.78133203177157</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_0</t>
+          <t>model_2_0_13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.386103030586224</v>
+        <v>0.6991677209449461</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2603517651366548</v>
+        <v>0.2021653923970157</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1260056079672193</v>
+        <v>-2.055493967256151</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.338251870752025</v>
+        <v>0.420976295828983</v>
       </c>
       <c r="F14" t="n">
-        <v>0.174528134616402</v>
+        <v>0.143650383589613</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3644357600122753</v>
+        <v>0.1785870361248818</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4390871433549584</v>
+        <v>0.4736290877336335</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2608420818690529</v>
+        <v>0.3240777349726138</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2729207000817127</v>
+        <v>0.3793996705322861</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2668813909753828</v>
+        <v>0.3517387027524499</v>
       </c>
       <c r="L14" t="n">
-        <v>0.410816983671278</v>
+        <v>0.2103842186055924</v>
       </c>
       <c r="M14" t="n">
-        <v>0.603685149736413</v>
+        <v>0.4225955940670487</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6370585851034027</v>
+        <v>0.1977805891865229</v>
       </c>
       <c r="O14" t="n">
-        <v>0.629385276361228</v>
+        <v>0.4405863633999604</v>
       </c>
       <c r="P14" t="n">
-        <v>32.0188099689174</v>
+        <v>33.44535839852225</v>
       </c>
       <c r="Q14" t="n">
-        <v>50.30194734194041</v>
+        <v>51.72849577154525</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_14</t>
+          <t>model_2_0_0</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8054599779098489</v>
+        <v>0.497290585265873</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2460140010978901</v>
+        <v>0.1795545768082757</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1268905641772233</v>
+        <v>-0.03237513581728901</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7862391087860533</v>
+        <v>0.5998997175129672</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4412927847240939</v>
+        <v>0.5475752864800469</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1154873608040947</v>
+        <v>0.2984300245021644</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4475986594475261</v>
+        <v>0.4870518446034852</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3363184975534188</v>
+        <v>0.1094977765438552</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02495016589527543</v>
+        <v>0.2621618325156179</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1806343317243471</v>
+        <v>0.1858298045297365</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1810260675313106</v>
+        <v>0.3890452412652369</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3398343137531799</v>
+        <v>0.5462874925368184</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4812266077595971</v>
+        <v>-0.3405584392910053</v>
       </c>
       <c r="O15" t="n">
-        <v>0.354301764043662</v>
+        <v>0.5695440820651165</v>
       </c>
       <c r="P15" t="n">
-        <v>34.31718837055159</v>
+        <v>32.41843959481874</v>
       </c>
       <c r="Q15" t="n">
-        <v>52.6003257435746</v>
+        <v>50.70157696784175</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_4</t>
+          <t>model_2_0_14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.590533638511197</v>
+        <v>0.6902729399423722</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1361058029452374</v>
+        <v>0.1635221197611998</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6121867015044891</v>
+        <v>-2.136706262484068</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.168280535561857</v>
+        <v>0.3762709057910569</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3160156078280958</v>
+        <v>0.09750648392863459</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2430769202055688</v>
+        <v>0.1838673623625423</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5128449136578875</v>
+        <v>0.4965694036727125</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4811542721732472</v>
+        <v>0.3326914311446358</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3698016251528563</v>
+        <v>0.4086924440909951</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4254779486630518</v>
+        <v>0.3706919376178155</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2594374641278364</v>
+        <v>0.2112744472861255</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4930283158253376</v>
+        <v>0.4287975773748521</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.09191029730347466</v>
+        <v>0.1740611731796591</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5140175519393334</v>
+        <v>0.4470523779770523</v>
       </c>
       <c r="P16" t="n">
-        <v>32.8287546833505</v>
+        <v>33.3870812760812</v>
       </c>
       <c r="Q16" t="n">
-        <v>51.11189205637351</v>
+        <v>51.67021864910421</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_7</t>
+          <t>model_2_0_15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7105363463503315</v>
+        <v>0.680447507039655</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04632638177354464</v>
+        <v>0.1295576867393348</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.342151704048862</v>
+        <v>-2.215812751983398</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2906333875926579</v>
+        <v>0.3296566026592342</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2524766769821029</v>
+        <v>0.05011186374490806</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1718381289851987</v>
+        <v>0.1897001637701965</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5661418563344607</v>
+        <v>0.5167321583016029</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4005628043607303</v>
+        <v>0.3410817772599644</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08279725332178997</v>
+        <v>0.4392360144541907</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2416800288412601</v>
+        <v>0.3901588958570775</v>
       </c>
       <c r="L17" t="n">
-        <v>0.220942030386464</v>
+        <v>0.214149880202216</v>
       </c>
       <c r="M17" t="n">
-        <v>0.414533628292324</v>
+        <v>0.4355458228133941</v>
       </c>
       <c r="N17" t="n">
-        <v>0.228096923600884</v>
+        <v>0.1478600187724133</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4321811830516358</v>
+        <v>0.4540879101947069</v>
       </c>
       <c r="P17" t="n">
-        <v>33.52240471168486</v>
+        <v>33.32462107746003</v>
       </c>
       <c r="Q17" t="n">
-        <v>51.80554208470787</v>
+        <v>51.60775845048304</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_5</t>
+          <t>model_2_0_16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5161097756630484</v>
+        <v>0.6698273420769507</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02466478985501985</v>
+        <v>0.09912540389172619</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6743390486261462</v>
+        <v>-2.295295134959596</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.428879118587131</v>
+        <v>0.2795577047184145</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7527609881549486</v>
+        <v>-0.0001107069051644594</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2872581401357055</v>
+        <v>0.1960047524592965</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5790011130293451</v>
+        <v>0.534798076006112</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4997035303424611</v>
+        <v>0.3495119921192277</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6336586354263296</v>
+        <v>0.4720628317949255</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5666810828843953</v>
+        <v>0.4107874119570766</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2589368283646669</v>
+        <v>0.217000405964688</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5359646817988154</v>
+        <v>0.4427242397467034</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2903739315652043</v>
+        <v>0.1195395788718686</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5587818079028326</v>
+        <v>0.4615719271982388</v>
       </c>
       <c r="P18" t="n">
-        <v>32.49474804899484</v>
+        <v>33.25923274560854</v>
       </c>
       <c r="Q18" t="n">
-        <v>50.77788542201785</v>
+        <v>51.54237011863155</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_8</t>
+          <t>model_2_0_17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7201374184437402</v>
+        <v>0.6581646637632761</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.02123782482473602</v>
+        <v>0.07109883114978877</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2717578997921395</v>
+        <v>-2.377904765304674</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3302278383421767</v>
+        <v>0.2242300392848382</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2921144147159396</v>
+        <v>-0.05490766726642748</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1661385178458322</v>
+        <v>0.2029282221077644</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6062508879929549</v>
+        <v>0.5514358602706291</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3795538978730129</v>
+        <v>0.3582738951620928</v>
       </c>
       <c r="J19" t="n">
-        <v>0.07817579001705449</v>
+        <v>0.5083157483605305</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2288648439450337</v>
+        <v>0.4332948217613117</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2180164611015834</v>
+        <v>0.2198935350654975</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4076009296429931</v>
+        <v>0.4504755510654984</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2536997825166407</v>
+        <v>0.08843910336873628</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4249533450681383</v>
+        <v>0.4696532278873012</v>
       </c>
       <c r="P19" t="n">
-        <v>33.58986678745347</v>
+        <v>33.18980589628508</v>
       </c>
       <c r="Q19" t="n">
-        <v>51.87300416047648</v>
+        <v>51.47294326930809</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_6</t>
+          <t>model_2_0_18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4670359879737142</v>
+        <v>0.6449682671904011</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.05211608117343203</v>
+        <v>0.04402806106774004</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6933538289496266</v>
+        <v>-2.467652723079025</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.974997015604592</v>
+        <v>0.1613024102186894</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.040625742708666</v>
+        <v>-0.1166882359508139</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3163904603853422</v>
+        <v>0.2107621731680726</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6245815548327616</v>
+        <v>0.5675062387877112</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5053784579290368</v>
+        <v>0.367792917351506</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8141214778348158</v>
+        <v>0.5495484674411008</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6597499678819263</v>
+        <v>0.4586706923963034</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2600618846435365</v>
+        <v>0.2230827625493211</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5624859646118667</v>
+        <v>0.4590884154148007</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4212373654034289</v>
+        <v>0.05324871250773633</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5864321566318594</v>
+        <v>0.4786327597030405</v>
       </c>
       <c r="P20" t="n">
-        <v>32.30155638806396</v>
+        <v>33.11404984518238</v>
       </c>
       <c r="Q20" t="n">
-        <v>50.58469376108697</v>
+        <v>51.39718721820539</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_9</t>
+          <t>model_2_0_19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7403807127100773</v>
+        <v>0.6295355933061813</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.1001187825745133</v>
+        <v>0.01603591354784983</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1562125278130173</v>
+        <v>-2.56933604656258</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3706955091314221</v>
+        <v>0.08760827158085216</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3527496863771303</v>
+        <v>-0.1885975036787588</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1541212239045548</v>
+        <v>0.219923675042545</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6530780319931728</v>
+        <v>0.584123586753329</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3450695857857587</v>
+        <v>0.3785778514774373</v>
       </c>
       <c r="J21" t="n">
-        <v>0.07345240449104397</v>
+        <v>0.5978358375745662</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2092609951384014</v>
+        <v>0.4882068445260017</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2114939115633577</v>
+        <v>0.2267099670782093</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3925827605799251</v>
+        <v>0.468960206246271</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3076819005602063</v>
+        <v>0.01209491548315</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4092958214561598</v>
+        <v>0.4889248131076306</v>
       </c>
       <c r="P21" t="n">
-        <v>33.74003163602304</v>
+        <v>33.02894944889854</v>
       </c>
       <c r="Q21" t="n">
-        <v>52.02316900904605</v>
+        <v>51.31208682192155</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_11</t>
+          <t>model_2_0_20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7667008482209092</v>
+        <v>0.6114040136003782</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1038092344597938</v>
+        <v>-0.01535555123343846</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2712970175527638</v>
+        <v>-2.68402501343224</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5183162215921544</v>
+        <v>0.000993298353508032</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3262788074720393</v>
+        <v>-0.2724920113950797</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1384964544946721</v>
+        <v>0.2306873639993702</v>
       </c>
       <c r="H22" t="n">
-        <v>0.655268843651496</v>
+        <v>0.6027589162881724</v>
       </c>
       <c r="I22" t="n">
-        <v>0.379416348383095</v>
+        <v>0.3907422154093504</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0562221186115392</v>
+        <v>0.654589459350146</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2178192334973171</v>
+        <v>0.5226658373797483</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2007771464055461</v>
+        <v>0.2306090539838256</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3721511178199954</v>
+        <v>0.4802992442211108</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3778689285890913</v>
+        <v>-0.03625596373232476</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3879943613646086</v>
+        <v>0.5007465774041039</v>
       </c>
       <c r="P22" t="n">
-        <v>33.95382110599772</v>
+        <v>32.93338377547391</v>
       </c>
       <c r="Q22" t="n">
-        <v>52.23695847902073</v>
+        <v>51.21652114849692</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_13</t>
+          <t>model_2_0_21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.778775212696494</v>
+        <v>0.5394018104375506</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1152219643272026</v>
+        <v>-0.273687376799141</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2198193775161967</v>
+        <v>-3.130020079199789</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5367936363174732</v>
+        <v>-0.3371904782549389</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3533738864819099</v>
+        <v>-0.5998211817581831</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1313285901565781</v>
+        <v>0.2734309821300488</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6620439331050497</v>
+        <v>0.7561158472977796</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3640529376801803</v>
+        <v>0.4380462102042425</v>
       </c>
       <c r="J23" t="n">
-        <v>0.05406543522528266</v>
+        <v>0.8761811014545132</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2090591864527315</v>
+        <v>0.6571136558293779</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1964685825714683</v>
+        <v>0.2364224931413585</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3623928671436265</v>
+        <v>0.5229062842709474</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4100672338573172</v>
+        <v>-0.2282618388331983</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3778206817545831</v>
+        <v>0.5451674873575938</v>
       </c>
       <c r="P23" t="n">
-        <v>34.06010554912709</v>
+        <v>32.59341207899168</v>
       </c>
       <c r="Q23" t="n">
-        <v>52.3432429221501</v>
+        <v>50.87654945201469</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_12</t>
+          <t>model_2_0_22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7755949129162063</v>
+        <v>0.4704307456286699</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1902506132394093</v>
+        <v>-0.5058745509063456</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1613126708480552</v>
+        <v>-3.503696797798781</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3951406750317497</v>
+        <v>-0.6689499135339543</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3548082679918982</v>
+        <v>-0.9126888919943774</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1332165534879541</v>
+        <v>0.3143751855954655</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7065841801682089</v>
+        <v>0.8939521838114857</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3465917144621168</v>
+        <v>0.4776798360183719</v>
       </c>
       <c r="J24" t="n">
-        <v>0.07059916533636501</v>
+        <v>1.093563256164469</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2085954398992409</v>
+        <v>0.7856215460914205</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1998086566306578</v>
+        <v>0.2362900600522262</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3649884292521532</v>
+        <v>0.5606917028059765</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4015864344432168</v>
+        <v>-0.4121846783235468</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3805267423156241</v>
+        <v>0.5845615093862584</v>
       </c>
       <c r="P24" t="n">
-        <v>34.03155850632462</v>
+        <v>32.31433629553</v>
       </c>
       <c r="Q24" t="n">
-        <v>52.31469587934763</v>
+        <v>50.59747366855301</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_2_0_10</t>
+          <t>model_2_0_23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7533498739068428</v>
+        <v>0.4037854597083056</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.2045529047242589</v>
+        <v>-0.7219437266272546</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1213578550325831</v>
+        <v>-3.807689147472781</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5347706485584727</v>
+        <v>-1.005036296645661</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3984540785317653</v>
+        <v>-1.22001077431661</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1464221695795623</v>
+        <v>0.3539387062442422</v>
       </c>
       <c r="H25" t="n">
-        <v>0.715074638220438</v>
+        <v>1.02222018022181</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3346672702860364</v>
+        <v>0.5099224629674349</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05430155830609754</v>
+        <v>1.31378060150705</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1944844142960669</v>
+        <v>0.9118515322372425</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2066051022575513</v>
+        <v>0.2388140776478086</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3826514988596834</v>
+        <v>0.5949274798193829</v>
       </c>
       <c r="N25" t="n">
-        <v>0.3422663304182476</v>
+        <v>-0.5899054407778517</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3989417653639415</v>
+        <v>0.6202547743049539</v>
       </c>
       <c r="P25" t="n">
-        <v>33.84252251473028</v>
+        <v>32.07726305408521</v>
       </c>
       <c r="Q25" t="n">
-        <v>52.12565988775329</v>
+        <v>50.36040042710822</v>
       </c>
     </row>
   </sheetData>
